--- a/web/files/港岛-半山区西部-帝汇豪庭.xlsx
+++ b/web/files/港岛-半山区西部-帝汇豪庭.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -127,6 +127,12 @@
     <font>
       <name val="Microsoft YaHei"/>
       <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
       <color rgb="00000000"/>
       <sz val="8"/>
     </font>
@@ -207,7 +213,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -275,7 +281,10 @@
     <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1529,7 +1538,7 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
@@ -1539,12 +1548,12 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1554,12 +1563,12 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
@@ -1569,7 +1578,7 @@
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -6801,14 +6810,14 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
           <t>39</t>
@@ -6821,7 +6830,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>41</t>
         </is>
       </c>
     </row>
@@ -6988,12 +6997,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D9" s="20" t="inlineStr">
+      <c r="D9" s="23" t="inlineStr">
         <is>
           <t>C | 1179呎 (3房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -7206,7 +7215,7 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B15" s="23" t="inlineStr">
+      <c r="B15" s="24" t="inlineStr">
         <is>
           <t>A | 1735呎 (4+房)
 -
@@ -7214,7 +7223,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="C15" s="23" t="inlineStr">
+      <c r="C15" s="24" t="inlineStr">
         <is>
           <t>B | 1023呎 (2房)
 -
@@ -7230,7 +7239,7 @@
 (16年-06月-06日)</t>
         </is>
       </c>
-      <c r="E15" s="23" t="inlineStr">
+      <c r="E15" s="24" t="inlineStr">
         <is>
           <t>D | 1702呎 (4+房)
 -
@@ -7245,7 +7254,7 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B16" s="23" t="inlineStr">
+      <c r="B16" s="24" t="inlineStr">
         <is>
           <t>A | 1735呎 (4+房)
 -
@@ -7253,7 +7262,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="C16" s="23" t="inlineStr">
+      <c r="C16" s="24" t="inlineStr">
         <is>
           <t>B | 1023呎 (2房)
 -
@@ -7284,7 +7293,7 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B17" s="23" t="inlineStr">
+      <c r="B17" s="24" t="inlineStr">
         <is>
           <t>A | 1735呎 (4+房)
 -
@@ -7292,7 +7301,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="C17" s="23" t="inlineStr">
+      <c r="C17" s="24" t="inlineStr">
         <is>
           <t>B | 1023呎 (2房)
 -
@@ -7425,7 +7434,7 @@
 (16年-03月-02日)</t>
         </is>
       </c>
-      <c r="E20" s="23" t="inlineStr">
+      <c r="E20" s="24" t="inlineStr">
         <is>
           <t>D | 1702呎 (4+房)
 -
@@ -7464,7 +7473,7 @@
 (16年-02月-22日)</t>
         </is>
       </c>
-      <c r="E21" s="23" t="inlineStr">
+      <c r="E21" s="24" t="inlineStr">
         <is>
           <t>D | 1702呎 (4+房)
 -

--- a/web/files/港岛-半山区西部-帝汇豪庭.xlsx
+++ b/web/files/港岛-半山区西部-帝汇豪庭.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -127,12 +127,6 @@
     <font>
       <name val="Microsoft YaHei"/>
       <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
       <color rgb="00000000"/>
       <sz val="8"/>
     </font>
@@ -213,7 +207,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -281,10 +275,7 @@
     <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1538,38 +1529,30 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>49283000</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>41801</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L14" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K14" s="5" t="n">
+        <v>49283000</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>41801</v>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
@@ -1578,7 +1561,7 @@
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -6810,7 +6793,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -6820,7 +6803,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -6997,12 +6980,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D9" s="23" t="inlineStr">
+      <c r="D9" s="22" t="inlineStr">
         <is>
           <t>C | 1179呎 (3房)
-招标单位
--
-(在售)</t>
+$4928万
+$41,801/呎
+(26年-09月-29日)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -7215,7 +7198,7 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B15" s="24" t="inlineStr">
+      <c r="B15" s="23" t="inlineStr">
         <is>
           <t>A | 1735呎 (4+房)
 -
@@ -7223,7 +7206,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="C15" s="24" t="inlineStr">
+      <c r="C15" s="23" t="inlineStr">
         <is>
           <t>B | 1023呎 (2房)
 -
@@ -7239,7 +7222,7 @@
 (16年-06月-06日)</t>
         </is>
       </c>
-      <c r="E15" s="24" t="inlineStr">
+      <c r="E15" s="23" t="inlineStr">
         <is>
           <t>D | 1702呎 (4+房)
 -
@@ -7254,7 +7237,7 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B16" s="24" t="inlineStr">
+      <c r="B16" s="23" t="inlineStr">
         <is>
           <t>A | 1735呎 (4+房)
 -
@@ -7262,7 +7245,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="C16" s="24" t="inlineStr">
+      <c r="C16" s="23" t="inlineStr">
         <is>
           <t>B | 1023呎 (2房)
 -
@@ -7293,7 +7276,7 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B17" s="24" t="inlineStr">
+      <c r="B17" s="23" t="inlineStr">
         <is>
           <t>A | 1735呎 (4+房)
 -
@@ -7301,7 +7284,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="C17" s="24" t="inlineStr">
+      <c r="C17" s="23" t="inlineStr">
         <is>
           <t>B | 1023呎 (2房)
 -
@@ -7434,7 +7417,7 @@
 (16年-03月-02日)</t>
         </is>
       </c>
-      <c r="E20" s="24" t="inlineStr">
+      <c r="E20" s="23" t="inlineStr">
         <is>
           <t>D | 1702呎 (4+房)
 -
@@ -7473,7 +7456,7 @@
 (16年-02月-22日)</t>
         </is>
       </c>
-      <c r="E21" s="24" t="inlineStr">
+      <c r="E21" s="23" t="inlineStr">
         <is>
           <t>D | 1702呎 (4+房)
 -

--- a/web/files/港岛-半山区西部-帝汇豪庭.xlsx
+++ b/web/files/港岛-半山区西部-帝汇豪庭.xlsx
@@ -1534,7 +1534,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -6985,7 +6985,7 @@
           <t>C | 1179呎 (3房)
 $4928万
 $41,801/呎
-(26年-09月-29日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">

--- a/web/files/港岛-半山区西部-帝汇豪庭.xlsx
+++ b/web/files/港岛-半山区西部-帝汇豪庭.xlsx
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>4686</v>
+        <v>4679</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>4754</v>
+        <v>4749</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>2718</v>
+        <v>2712</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>2718</v>
+        <v>2712</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>41800000</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>40820</v>
+        <v>40860</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
         <v>41800000</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>40820</v>
+        <v>40860</v>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>39897000</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>38962</v>
+        <v>39000</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
         <v>39897000</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>38962</v>
+        <v>39000</v>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
@@ -4515,7 +4515,7 @@
         </is>
       </c>
       <c r="E59" s="4" t="n">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
         <v>33218800</v>
       </c>
       <c r="I59" s="5" t="n">
-        <v>32440</v>
+        <v>32472</v>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
@@ -4542,7 +4542,7 @@
         <v>33218800</v>
       </c>
       <c r="L59" s="5" t="n">
-        <v>32440</v>
+        <v>32472</v>
       </c>
       <c r="M59" s="3" t="inlineStr">
         <is>
@@ -4771,7 +4771,7 @@
         </is>
       </c>
       <c r="E63" s="4" t="n">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
@@ -4787,7 +4787,7 @@
         <v>32408600</v>
       </c>
       <c r="I63" s="5" t="n">
-        <v>31649</v>
+        <v>31680</v>
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
@@ -4798,7 +4798,7 @@
         <v>32408600</v>
       </c>
       <c r="L63" s="5" t="n">
-        <v>31649</v>
+        <v>31680</v>
       </c>
       <c r="M63" s="3" t="inlineStr">
         <is>
@@ -5035,7 +5035,7 @@
         </is>
       </c>
       <c r="E67" s="4" t="n">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>31902700</v>
       </c>
       <c r="I67" s="5" t="n">
-        <v>31155</v>
+        <v>31185</v>
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
@@ -5062,7 +5062,7 @@
         <v>31902700</v>
       </c>
       <c r="L67" s="5" t="n">
-        <v>31155</v>
+        <v>31185</v>
       </c>
       <c r="M67" s="3" t="inlineStr">
         <is>
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
@@ -5587,7 +5587,7 @@
         <v>24347000</v>
       </c>
       <c r="I75" s="5" t="n">
-        <v>23776</v>
+        <v>23800</v>
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
         <v>24347000</v>
       </c>
       <c r="L75" s="5" t="n">
-        <v>23776</v>
+        <v>23800</v>
       </c>
       <c r="M75" s="3" t="inlineStr">
         <is>
@@ -6091,7 +6091,7 @@
         </is>
       </c>
       <c r="E83" s="4" t="n">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
@@ -6107,7 +6107,7 @@
         <v>30383100</v>
       </c>
       <c r="I83" s="5" t="n">
-        <v>29671</v>
+        <v>29700</v>
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
@@ -6118,7 +6118,7 @@
         <v>30383100</v>
       </c>
       <c r="L83" s="5" t="n">
-        <v>29671</v>
+        <v>29700</v>
       </c>
       <c r="M83" s="3" t="inlineStr">
         <is>
@@ -6347,7 +6347,7 @@
         </is>
       </c>
       <c r="E87" s="4" t="n">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
@@ -6852,7 +6852,7 @@
       </c>
       <c r="B5" s="20" t="inlineStr">
         <is>
-          <t>A | 4754呎 (4+房)
+          <t>A | 4749呎 (4+房)
 -
 -
 (待售)</t>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C5" s="20" t="inlineStr">
         <is>
-          <t>B | 4686呎 (4+房)
+          <t>B | 4679呎 (4+房)
 -
 -
 (待售)</t>
@@ -6877,7 +6877,7 @@
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>A | 2718呎 (4+房)
+          <t>A | 2712呎 (4+房)
 -
 -
 (待售)</t>
@@ -6902,7 +6902,7 @@
       </c>
       <c r="B7" s="20" t="inlineStr">
         <is>
-          <t>A | 2718呎 (4+房)
+          <t>A | 2712呎 (4+房)
 -
 -
 (待售)</t>
@@ -6974,7 +6974,7 @@
       </c>
       <c r="C9" s="20" t="inlineStr">
         <is>
-          <t>B | 1024呎 (2房)
+          <t>B | 1023呎 (2房)
 -
 -
 (待售)</t>
@@ -7013,9 +7013,9 @@
       </c>
       <c r="C10" s="22" t="inlineStr">
         <is>
-          <t>B | 1024呎 (2房)
+          <t>B | 1023呎 (2房)
 $4180万
-$40,820/呎
+$40,860/呎
 (24年-11月-07日)</t>
         </is>
       </c>
@@ -7052,9 +7052,9 @@
       </c>
       <c r="C11" s="22" t="inlineStr">
         <is>
-          <t>B | 1024呎 (2房)
+          <t>B | 1023呎 (2房)
 $3990万
-$38,962/呎
+$39,000/呎
 (25年-10月-21日)</t>
         </is>
       </c>
@@ -7403,9 +7403,9 @@
       </c>
       <c r="C20" s="22" t="inlineStr">
         <is>
-          <t>B | 1024呎 (2房)
+          <t>B | 1023呎 (2房)
 $3322万
-$32,440/呎
+$32,472/呎
 (24年-05月-29日)</t>
         </is>
       </c>
@@ -7442,9 +7442,9 @@
       </c>
       <c r="C21" s="22" t="inlineStr">
         <is>
-          <t>B | 1024呎 (2房)
+          <t>B | 1023呎 (2房)
 $3241万
-$31,649/呎
+$31,680/呎
 (24年-05月-02日)</t>
         </is>
       </c>
@@ -7481,9 +7481,9 @@
       </c>
       <c r="C22" s="22" t="inlineStr">
         <is>
-          <t>B | 1024呎 (2房)
+          <t>B | 1023呎 (2房)
 $3190万
-$31,155/呎
+$31,185/呎
 (24年-10月-16日)</t>
         </is>
       </c>
@@ -7559,9 +7559,9 @@
       </c>
       <c r="C24" s="22" t="inlineStr">
         <is>
-          <t>B | 1024呎 (2房)
+          <t>B | 1023呎 (2房)
 $2435万
-$23,776/呎
+$23,800/呎
 (16年-02月-22日)</t>
         </is>
       </c>
@@ -7637,9 +7637,9 @@
       </c>
       <c r="C26" s="22" t="inlineStr">
         <is>
-          <t>B | 1024呎 (2房)
+          <t>B | 1023呎 (2房)
 $3038万
-$29,671/呎
+$29,700/呎
 (24年-04月-24日)</t>
         </is>
       </c>
@@ -7676,7 +7676,7 @@
       </c>
       <c r="C27" s="20" t="inlineStr">
         <is>
-          <t>B | 1024呎 (2房)
+          <t>B | 1023呎 (2房)
 -
 -
 (待售)</t>
